--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5192" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5194" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,7 +486,12 @@
     <t>Prescription</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `Immunization.basedOn` (new:Reference(CarePlan,MedicationRequest,ServiceRequest,ImmunizationRecommendation))</t>
+  </si>
+  <si>
+    <t>Element `Immunization.basedOn` has a context of Immunization based on following the parent source element upwards and mapping to `Immunization`.
+Element `Immunization.basedOn` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+Allows tracing of an authorization for the Immunization.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -558,10 +563,13 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Authority that the immunization event is based on</t>
+  </si>
+  <si>
+    <t>A plan, order or recommendation fulfilled in whole or in part by this immunization.</t>
+  </si>
+  <si>
+    <t>Allows tracing of an authorization for the Immunization.</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1447,6 +1455,12 @@
   </si>
   <si>
     <t>Immunization.performer.actor.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>AUT</t>
@@ -3591,7 +3605,9 @@
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>78</v>
@@ -3649,7 +3665,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3661,7 +3677,7 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>78</v>
@@ -3672,10 +3688,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3698,13 +3714,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3755,7 +3771,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3776,7 +3792,7 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -3787,10 +3803,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3861,7 +3877,7 @@
         <v>137</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>78</v>
@@ -3870,7 +3886,7 @@
         <v>138</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3902,10 +3918,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3931,13 +3947,13 @@
         <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3945,7 +3961,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>78</v>
@@ -3987,7 +4003,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>89</v>
@@ -4019,10 +4035,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4045,15 +4061,17 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -4102,7 +4120,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4134,14 +4152,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4163,16 +4181,16 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -4221,7 +4239,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4253,10 +4271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4279,13 +4297,13 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4336,7 +4354,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4351,27 +4369,27 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4397,13 +4415,13 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4414,7 +4432,7 @@
         <v>78</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>78</v>
@@ -4429,13 +4447,13 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
@@ -4453,7 +4471,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -4468,16 +4486,16 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4485,10 +4503,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4511,16 +4529,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4546,13 +4564,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -4570,7 +4588,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4585,13 +4603,13 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4602,10 +4620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4628,13 +4646,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4661,13 +4679,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -4685,7 +4703,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4700,27 +4718,27 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4743,13 +4761,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4800,7 +4818,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4821,7 +4839,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4832,14 +4850,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4861,13 +4879,13 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4908,7 +4926,7 @@
         <v>137</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
@@ -4917,7 +4935,7 @@
         <v>138</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4938,7 +4956,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4949,10 +4967,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4975,19 +4993,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -5024,10 +5042,10 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
@@ -5036,7 +5054,7 @@
         <v>138</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5054,10 +5072,10 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -5068,13 +5086,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -5096,19 +5114,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -5157,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5175,10 +5193,10 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -5189,10 +5207,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5215,13 +5233,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5272,7 +5290,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5293,7 +5311,7 @@
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -5304,14 +5322,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5333,13 +5351,13 @@
         <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5380,7 +5398,7 @@
         <v>137</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
@@ -5389,7 +5407,7 @@
         <v>138</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5410,7 +5428,7 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5421,10 +5439,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5450,16 +5468,16 @@
         <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5469,7 +5487,7 @@
         <v>78</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>78</v>
@@ -5508,7 +5526,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5526,10 +5544,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5540,10 +5558,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5566,16 +5584,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5625,7 +5643,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5643,10 +5661,10 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5657,10 +5675,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5686,14 +5704,14 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5742,7 +5760,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5760,10 +5778,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5774,10 +5792,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5800,17 +5818,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5859,7 +5877,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5877,10 +5895,10 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5891,10 +5909,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5917,19 +5935,19 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5978,7 +5996,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5996,10 +6014,10 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -6010,13 +6028,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -6038,19 +6056,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -6075,11 +6093,11 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -6097,7 +6115,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6115,10 +6133,10 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -6129,10 +6147,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6155,13 +6173,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6212,7 +6230,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6233,7 +6251,7 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -6244,14 +6262,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6273,13 +6291,13 @@
         <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6320,7 +6338,7 @@
         <v>137</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>78</v>
@@ -6329,7 +6347,7 @@
         <v>138</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6350,7 +6368,7 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -6361,10 +6379,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6390,16 +6408,16 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6448,7 +6466,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6466,10 +6484,10 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6480,10 +6498,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6506,16 +6524,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6565,7 +6583,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6583,10 +6601,10 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6597,10 +6615,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6626,14 +6644,14 @@
         <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6682,7 +6700,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6700,10 +6718,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6714,10 +6732,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6740,17 +6758,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6799,7 +6817,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6817,10 +6835,10 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6831,10 +6849,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6857,19 +6875,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6918,7 +6936,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6936,10 +6954,10 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6950,10 +6968,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6976,19 +6994,19 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7037,7 +7055,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7055,10 +7073,10 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -7069,10 +7087,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7095,13 +7113,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7152,7 +7170,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>89</v>
@@ -7167,16 +7185,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7184,10 +7202,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7210,13 +7228,13 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7267,7 +7285,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7282,16 +7300,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7299,10 +7317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7325,16 +7343,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7384,7 +7402,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>89</v>
@@ -7399,27 +7417,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7442,13 +7460,13 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7499,7 +7517,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7531,10 +7549,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7612,7 +7630,7 @@
         <v>138</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7644,13 +7662,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7672,13 +7690,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7729,7 +7747,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7750,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7761,10 +7779,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7787,13 +7805,13 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7844,7 +7862,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7876,10 +7894,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7902,13 +7920,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7959,7 +7977,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7980,10 +7998,10 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7991,10 +8009,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8017,16 +8035,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8076,7 +8094,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8094,13 +8112,13 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8108,10 +8126,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8134,16 +8152,16 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8169,13 +8187,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8193,7 +8211,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8211,13 +8229,13 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8225,10 +8243,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8251,13 +8269,13 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8308,7 +8326,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8323,16 +8341,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8340,10 +8358,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8366,13 +8384,13 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8423,7 +8441,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8441,24 +8459,24 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8481,13 +8499,13 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8538,7 +8556,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8556,24 +8574,24 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8596,13 +8614,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8653,7 +8671,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8671,10 +8689,10 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8685,10 +8703,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8711,13 +8729,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8744,11 +8762,11 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8766,7 +8784,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8784,24 +8802,24 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8824,13 +8842,13 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8857,11 +8875,11 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8879,7 +8897,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8897,24 +8915,24 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8937,13 +8955,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8994,7 +9012,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9012,10 +9030,10 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -9026,10 +9044,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9052,13 +9070,13 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9109,7 +9127,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9124,13 +9142,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9141,10 +9159,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9167,13 +9185,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9224,7 +9242,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9245,7 +9263,7 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9256,14 +9274,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9285,13 +9303,13 @@
         <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9341,7 +9359,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9362,7 +9380,7 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9373,14 +9391,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9402,16 +9420,16 @@
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9460,7 +9478,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9492,10 +9510,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9518,13 +9536,13 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9551,13 +9569,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9575,7 +9593,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9590,13 +9608,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9607,10 +9625,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9633,16 +9651,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9692,7 +9710,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>89</v>
@@ -9707,16 +9725,16 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9724,10 +9742,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9750,13 +9768,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9807,7 +9825,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9828,7 +9846,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9839,10 +9857,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9913,7 +9931,7 @@
         <v>137</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>78</v>
@@ -9922,7 +9940,7 @@
         <v>138</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9954,13 +9972,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>78</v>
@@ -9982,13 +10000,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10039,7 +10057,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10071,10 +10089,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10097,13 +10115,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10154,7 +10172,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10175,7 +10193,7 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -10186,10 +10204,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10197,7 +10215,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>80</v>
@@ -10260,7 +10278,7 @@
         <v>137</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
@@ -10269,7 +10287,7 @@
         <v>138</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10301,13 +10319,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>78</v>
@@ -10386,7 +10404,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10418,10 +10436,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10444,13 +10462,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10501,7 +10519,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10522,7 +10540,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10533,10 +10551,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10607,7 +10625,7 @@
         <v>137</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
@@ -10616,7 +10634,7 @@
         <v>138</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10648,10 +10666,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10677,13 +10695,13 @@
         <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10691,7 +10709,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>78</v>
@@ -10733,7 +10751,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>89</v>
@@ -10765,10 +10783,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10794,10 +10812,10 @@
         <v>109</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10809,7 +10827,7 @@
         <v>78</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>78</v>
@@ -10824,11 +10842,11 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10846,7 +10864,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10878,13 +10896,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>78</v>
@@ -10909,7 +10927,7 @@
         <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>136</v>
@@ -10963,7 +10981,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10995,10 +11013,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11021,13 +11039,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11078,7 +11096,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11099,7 +11117,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11110,10 +11128,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11184,7 +11202,7 @@
         <v>137</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>78</v>
@@ -11193,7 +11211,7 @@
         <v>138</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11225,10 +11243,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11254,13 +11272,13 @@
         <v>103</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11268,7 +11286,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>78</v>
@@ -11310,7 +11328,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>89</v>
@@ -11342,10 +11360,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11368,13 +11386,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11425,7 +11443,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11457,13 +11475,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11542,7 +11560,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11574,10 +11592,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11600,13 +11618,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11657,7 +11675,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11678,7 +11696,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11689,10 +11707,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11763,7 +11781,7 @@
         <v>137</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
@@ -11772,7 +11790,7 @@
         <v>138</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11804,10 +11822,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11833,13 +11851,13 @@
         <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11847,7 +11865,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>78</v>
@@ -11889,7 +11907,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>89</v>
@@ -11921,10 +11939,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11947,13 +11965,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12004,7 +12022,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12036,10 +12054,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12065,13 +12083,13 @@
         <v>103</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12079,7 +12097,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>78</v>
@@ -12121,7 +12139,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>89</v>
@@ -12153,10 +12171,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12179,13 +12197,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12236,7 +12254,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12268,13 +12286,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>78</v>
@@ -12296,13 +12314,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12353,7 +12371,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12385,10 +12403,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12411,13 +12429,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12468,7 +12486,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12489,7 +12507,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12500,10 +12518,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12511,7 +12529,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>80</v>
@@ -12574,7 +12592,7 @@
         <v>137</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>78</v>
@@ -12583,7 +12601,7 @@
         <v>138</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12615,13 +12633,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>78</v>
@@ -12700,7 +12718,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12732,10 +12750,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12758,13 +12776,13 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12815,7 +12833,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12836,7 +12854,7 @@
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>78</v>
@@ -12847,10 +12865,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12921,7 +12939,7 @@
         <v>137</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>78</v>
@@ -12930,7 +12948,7 @@
         <v>138</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12962,10 +12980,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12991,13 +13009,13 @@
         <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13005,7 +13023,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>78</v>
@@ -13047,7 +13065,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>89</v>
@@ -13079,10 +13097,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13108,10 +13126,10 @@
         <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13123,7 +13141,7 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>78</v>
@@ -13138,11 +13156,11 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -13160,7 +13178,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13192,13 +13210,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>78</v>
@@ -13223,7 +13241,7 @@
         <v>134</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>136</v>
@@ -13277,7 +13295,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13309,10 +13327,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13335,13 +13353,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13392,7 +13410,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13413,7 +13431,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13424,10 +13442,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13498,7 +13516,7 @@
         <v>137</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
@@ -13507,7 +13525,7 @@
         <v>138</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13539,10 +13557,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13568,13 +13586,13 @@
         <v>103</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13582,7 +13600,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>78</v>
@@ -13624,7 +13642,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>89</v>
@@ -13656,10 +13674,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13682,13 +13700,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13739,7 +13757,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13771,13 +13789,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>78</v>
@@ -13856,7 +13874,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13888,10 +13906,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13914,13 +13932,13 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13971,7 +13989,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13992,7 +14010,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14003,10 +14021,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14077,7 +14095,7 @@
         <v>137</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
@@ -14086,7 +14104,7 @@
         <v>138</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14118,10 +14136,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14147,13 +14165,13 @@
         <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14161,7 +14179,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>78</v>
@@ -14203,7 +14221,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>89</v>
@@ -14235,10 +14253,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14261,13 +14279,13 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14318,7 +14336,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14350,10 +14368,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14379,13 +14397,13 @@
         <v>103</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14393,7 +14411,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>78</v>
@@ -14435,7 +14453,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>89</v>
@@ -14467,10 +14485,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14493,13 +14511,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>173</v>
+        <v>465</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14550,7 +14568,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14582,10 +14600,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14608,16 +14626,16 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14667,7 +14685,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14676,7 +14694,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -14699,10 +14717,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14728,13 +14746,13 @@
         <v>103</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14760,13 +14778,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14784,7 +14802,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14816,10 +14834,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14842,16 +14860,16 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14901,7 +14919,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14922,7 +14940,7 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14933,10 +14951,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14959,16 +14977,16 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15018,7 +15036,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15050,10 +15068,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15076,13 +15094,13 @@
         <v>90</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15133,7 +15151,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15148,13 +15166,13 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15165,10 +15183,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15191,13 +15209,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15224,31 +15242,31 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="Z111" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15263,13 +15281,13 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>78</v>
@@ -15280,10 +15298,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15306,13 +15324,13 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15363,7 +15381,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15378,7 +15396,7 @@
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>78</v>
@@ -15395,10 +15413,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15421,68 +15439,68 @@
         <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q113" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="R113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15500,7 +15518,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>132</v>
@@ -15514,10 +15532,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15540,13 +15558,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15573,31 +15591,31 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="Z114" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15629,10 +15647,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15655,13 +15673,13 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15712,7 +15730,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15724,7 +15742,7 @@
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
@@ -15744,10 +15762,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15770,13 +15788,13 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15827,7 +15845,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15848,7 +15866,7 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -15859,14 +15877,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15888,13 +15906,13 @@
         <v>134</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15944,7 +15962,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15965,7 +15983,7 @@
         <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -15976,14 +15994,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16005,16 +16023,16 @@
         <v>134</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>78</v>
@@ -16063,7 +16081,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16095,10 +16113,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16121,13 +16139,13 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16178,7 +16196,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16196,7 +16214,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>132</v>
@@ -16210,10 +16228,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16239,10 +16257,10 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16293,7 +16311,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16325,10 +16343,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16351,13 +16369,13 @@
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16408,7 +16426,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16426,7 +16444,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>132</v>
@@ -16440,10 +16458,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16466,13 +16484,13 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16523,7 +16541,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16541,7 +16559,7 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>132</v>
@@ -16555,10 +16573,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16581,13 +16599,13 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16614,31 +16632,31 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="Z123" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16656,7 +16674,7 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>132</v>
@@ -16670,10 +16688,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16696,13 +16714,13 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16729,31 +16747,31 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="Z124" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16785,10 +16803,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16811,16 +16829,16 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16870,7 +16888,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16888,10 +16906,10 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>78</v>
@@ -16902,10 +16920,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16928,13 +16946,13 @@
         <v>78</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16985,7 +17003,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17006,7 +17024,7 @@
         <v>78</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -17017,14 +17035,14 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17046,13 +17064,13 @@
         <v>134</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17102,7 +17120,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17123,7 +17141,7 @@
         <v>78</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>78</v>
@@ -17134,14 +17152,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17163,16 +17181,16 @@
         <v>134</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17221,7 +17239,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17253,10 +17271,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17279,13 +17297,13 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17336,7 +17354,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17354,10 +17372,10 @@
         <v>78</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17368,10 +17386,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17394,13 +17412,13 @@
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17451,7 +17469,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17469,10 +17487,10 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17483,10 +17501,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17509,13 +17527,13 @@
         <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17566,7 +17584,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17584,10 +17602,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -17598,10 +17616,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17624,13 +17642,13 @@
         <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17681,7 +17699,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17713,10 +17731,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17739,13 +17757,13 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17796,7 +17814,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17817,7 +17835,7 @@
         <v>78</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -17828,14 +17846,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -17857,13 +17875,13 @@
         <v>134</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17913,7 +17931,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17934,7 +17952,7 @@
         <v>78</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -17945,14 +17963,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -17974,16 +17992,16 @@
         <v>134</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18032,7 +18050,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18064,10 +18082,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18090,13 +18108,13 @@
         <v>78</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18123,11 +18141,11 @@
         <v>78</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>78</v>
@@ -18145,7 +18163,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18177,10 +18195,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18203,13 +18221,13 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18260,7 +18278,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18292,10 +18310,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18318,13 +18336,13 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18351,31 +18369,31 @@
         <v>78</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="Z138" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF138" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18407,10 +18425,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18433,16 +18451,16 @@
         <v>78</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18480,7 +18498,7 @@
         <v>78</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
@@ -18490,7 +18508,7 @@
         <v>138</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>89</v>
@@ -18522,13 +18540,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>78</v>
@@ -18550,16 +18568,16 @@
         <v>78</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N140" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18609,7 +18627,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>89</v>
@@ -18641,10 +18659,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18667,16 +18685,16 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -18726,7 +18744,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
